--- a/Check.xlsx
+++ b/Check.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavel\Desktop\мои кейсы\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavel\DiplomaProjectQA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B439996E-5AC9-4394-9126-5B7CE03F3DA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52311D22-D0F0-4C34-A375-2FEB200A94BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-113" yWindow="-113" windowWidth="32281" windowHeight="17656" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3306" yWindow="2029" windowWidth="23278" windowHeight="15076" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -411,13 +411,13 @@
     <t>Фильтрация новостей по чек-боксу "Не активна" во вкладке "Панель управления"</t>
   </si>
   <si>
-    <t>Развертывание и свернутывание цитаты в разделе Тематических цитат</t>
-  </si>
-  <si>
     <t>Переход по ссылке "Политика конфиденциальности" в разделе "О приложении"</t>
   </si>
   <si>
     <t>Переход по ссылке "Пользовательское соглашение" в разделе "О приложении"</t>
+  </si>
+  <si>
+    <t>Развертывание цитаты в разделе Тематических цитат</t>
   </si>
 </sst>
 </file>
@@ -1002,30 +1002,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1044,6 +1020,30 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1347,25 +1347,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="9" customFormat="1" ht="15.65" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="F1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="56"/>
+      <c r="G1" s="48"/>
     </row>
     <row r="2" spans="1:7" ht="25.7" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
@@ -1388,7 +1388,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="52" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="13">
@@ -1408,7 +1408,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A4" s="45"/>
+      <c r="A4" s="52"/>
       <c r="B4" s="6">
         <v>3</v>
       </c>
@@ -1426,7 +1426,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A5" s="45"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="6">
         <v>4</v>
       </c>
@@ -1444,7 +1444,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A6" s="45"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="6">
         <v>5</v>
       </c>
@@ -1462,7 +1462,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="25.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="46"/>
+      <c r="A7" s="53"/>
       <c r="B7" s="17">
         <v>6</v>
       </c>
@@ -1480,7 +1480,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="44" t="s">
+      <c r="A8" s="51" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="15">
@@ -1500,7 +1500,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="6">
         <v>8</v>
       </c>
@@ -1518,7 +1518,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="6">
         <v>9</v>
       </c>
@@ -1536,7 +1536,7 @@
       </c>
     </row>
     <row r="11" spans="1:7" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A11" s="45"/>
+      <c r="A11" s="52"/>
       <c r="B11" s="6">
         <v>10</v>
       </c>
@@ -1554,7 +1554,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="25.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="46"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="17">
         <v>11</v>
       </c>
@@ -1692,7 +1692,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="44" t="s">
+      <c r="A19" s="51" t="s">
         <v>60</v>
       </c>
       <c r="B19" s="15">
@@ -1712,7 +1712,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="45"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="6">
         <v>19</v>
       </c>
@@ -1730,7 +1730,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="6">
         <v>20</v>
       </c>
@@ -1748,7 +1748,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="45"/>
+      <c r="A22" s="52"/>
       <c r="B22" s="6">
         <v>21</v>
       </c>
@@ -1766,7 +1766,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="45"/>
+      <c r="A23" s="52"/>
       <c r="B23" s="6">
         <v>22</v>
       </c>
@@ -1784,7 +1784,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="45"/>
+      <c r="A24" s="52"/>
       <c r="B24" s="6">
         <v>23</v>
       </c>
@@ -1802,7 +1802,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="45"/>
+      <c r="A25" s="52"/>
       <c r="B25" s="6">
         <v>24</v>
       </c>
@@ -1820,7 +1820,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
+      <c r="A26" s="52"/>
       <c r="B26" s="6">
         <v>25</v>
       </c>
@@ -1838,7 +1838,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="45"/>
+      <c r="A27" s="52"/>
       <c r="B27" s="6">
         <v>26</v>
       </c>
@@ -1856,7 +1856,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="45"/>
+      <c r="A28" s="52"/>
       <c r="B28" s="6">
         <v>27</v>
       </c>
@@ -1874,7 +1874,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="45"/>
+      <c r="A29" s="52"/>
       <c r="B29" s="6">
         <v>28</v>
       </c>
@@ -1892,7 +1892,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="45"/>
+      <c r="A30" s="52"/>
       <c r="B30" s="6">
         <v>29</v>
       </c>
@@ -1910,7 +1910,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A31" s="50"/>
+      <c r="A31" s="57"/>
       <c r="B31" s="6">
         <v>30</v>
       </c>
@@ -2188,7 +2188,7 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A45" s="51" t="s">
+      <c r="A45" s="58" t="s">
         <v>74</v>
       </c>
       <c r="B45" s="6">
@@ -2208,7 +2208,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="50"/>
+      <c r="A46" s="57"/>
       <c r="B46" s="6">
         <v>45</v>
       </c>
@@ -2226,7 +2226,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="51" t="s">
+      <c r="A47" s="58" t="s">
         <v>75</v>
       </c>
       <c r="B47" s="6">
@@ -2246,7 +2246,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" ht="50.1" x14ac:dyDescent="0.3">
-      <c r="A48" s="45"/>
+      <c r="A48" s="52"/>
       <c r="B48" s="6">
         <v>47</v>
       </c>
@@ -2264,7 +2264,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" ht="50.1" x14ac:dyDescent="0.3">
-      <c r="A49" s="50"/>
+      <c r="A49" s="57"/>
       <c r="B49" s="6">
         <v>48</v>
       </c>
@@ -2329,7 +2329,7 @@
         <v>51</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D52" s="28" t="s">
         <v>4</v>
@@ -2338,18 +2338,18 @@
         <v>5</v>
       </c>
       <c r="F52" s="34" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="44" t="s">
+      <c r="A53" s="51" t="s">
         <v>79</v>
       </c>
       <c r="B53" s="15">
         <v>52</v>
       </c>
       <c r="C53" s="14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D53" s="15" t="s">
         <v>4</v>
@@ -2362,12 +2362,12 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="46"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="17">
         <v>53</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D54" s="17" t="s">
         <v>4</v>
@@ -2380,7 +2380,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" ht="23.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="47" t="s">
+      <c r="A55" s="54" t="s">
         <v>80</v>
       </c>
       <c r="B55" s="29">
@@ -2400,7 +2400,7 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="23.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="48"/>
+      <c r="A56" s="55"/>
       <c r="B56" s="12">
         <v>55</v>
       </c>
@@ -2418,7 +2418,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" ht="23.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="48"/>
+      <c r="A57" s="55"/>
       <c r="B57" s="12">
         <v>56</v>
       </c>
@@ -2436,7 +2436,7 @@
       </c>
     </row>
     <row r="58" spans="1:6" ht="23.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="48"/>
+      <c r="A58" s="55"/>
       <c r="B58" s="12">
         <v>57</v>
       </c>
@@ -2454,7 +2454,7 @@
       </c>
     </row>
     <row r="59" spans="1:6" ht="25.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="49"/>
+      <c r="A59" s="56"/>
       <c r="B59" s="30">
         <v>58</v>
       </c>
@@ -2472,7 +2472,7 @@
       </c>
     </row>
     <row r="60" spans="1:6" ht="15.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="44" t="s">
+      <c r="A60" s="51" t="s">
         <v>81</v>
       </c>
       <c r="B60" s="15">
@@ -2492,7 +2492,7 @@
       </c>
     </row>
     <row r="61" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A61" s="45"/>
+      <c r="A61" s="52"/>
       <c r="B61" s="6">
         <v>60</v>
       </c>
@@ -2510,7 +2510,7 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="45"/>
+      <c r="A62" s="52"/>
       <c r="B62" s="6">
         <v>61</v>
       </c>
@@ -2528,7 +2528,7 @@
       </c>
     </row>
     <row r="63" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A63" s="45"/>
+      <c r="A63" s="52"/>
       <c r="B63" s="6">
         <v>62</v>
       </c>
@@ -2546,7 +2546,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A64" s="45"/>
+      <c r="A64" s="52"/>
       <c r="B64" s="6">
         <v>63</v>
       </c>
@@ -2564,7 +2564,7 @@
       </c>
     </row>
     <row r="65" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A65" s="45"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="6">
         <v>64</v>
       </c>
@@ -2582,7 +2582,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A66" s="45"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="6">
         <v>65</v>
       </c>
@@ -2600,7 +2600,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A67" s="45"/>
+      <c r="A67" s="52"/>
       <c r="B67" s="6">
         <v>66</v>
       </c>
@@ -2618,7 +2618,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A68" s="45"/>
+      <c r="A68" s="52"/>
       <c r="B68" s="6">
         <v>67</v>
       </c>
@@ -2636,7 +2636,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A69" s="45"/>
+      <c r="A69" s="52"/>
       <c r="B69" s="6">
         <v>68</v>
       </c>
@@ -2654,7 +2654,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A70" s="45"/>
+      <c r="A70" s="52"/>
       <c r="B70" s="6">
         <v>69</v>
       </c>
@@ -2672,7 +2672,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A71" s="45"/>
+      <c r="A71" s="52"/>
       <c r="B71" s="6">
         <v>70</v>
       </c>
@@ -2690,7 +2690,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A72" s="45"/>
+      <c r="A72" s="52"/>
       <c r="B72" s="6">
         <v>71</v>
       </c>
@@ -2708,7 +2708,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="45"/>
+      <c r="A73" s="52"/>
       <c r="B73" s="6">
         <v>72</v>
       </c>
@@ -2726,7 +2726,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="37.6" x14ac:dyDescent="0.3">
-      <c r="A74" s="45"/>
+      <c r="A74" s="52"/>
       <c r="B74" s="6">
         <v>73</v>
       </c>
@@ -2744,7 +2744,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="45"/>
+      <c r="A75" s="52"/>
       <c r="B75" s="6">
         <v>74</v>
       </c>
@@ -2762,7 +2762,7 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="45"/>
+      <c r="A76" s="52"/>
       <c r="B76" s="6">
         <v>75</v>
       </c>
@@ -2780,7 +2780,7 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A77" s="45"/>
+      <c r="A77" s="52"/>
       <c r="B77" s="6">
         <v>76</v>
       </c>
@@ -2798,7 +2798,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A78" s="45"/>
+      <c r="A78" s="52"/>
       <c r="B78" s="6">
         <v>77</v>
       </c>
@@ -2816,7 +2816,7 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="45"/>
+      <c r="A79" s="52"/>
       <c r="B79" s="6">
         <v>78</v>
       </c>
@@ -2834,7 +2834,7 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="45"/>
+      <c r="A80" s="52"/>
       <c r="B80" s="6">
         <v>79</v>
       </c>
@@ -2852,7 +2852,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" ht="25.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="45"/>
+      <c r="A81" s="52"/>
       <c r="B81" s="38">
         <v>80</v>
       </c>
@@ -2870,7 +2870,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A82" s="47" t="s">
+      <c r="A82" s="54" t="s">
         <v>82</v>
       </c>
       <c r="B82" s="15">
@@ -2890,7 +2890,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A83" s="48"/>
+      <c r="A83" s="55"/>
       <c r="B83" s="6">
         <v>82</v>
       </c>
@@ -2908,7 +2908,7 @@
       </c>
     </row>
     <row r="84" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A84" s="48"/>
+      <c r="A84" s="55"/>
       <c r="B84" s="6">
         <v>83</v>
       </c>
@@ -2926,7 +2926,7 @@
       </c>
     </row>
     <row r="85" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A85" s="48"/>
+      <c r="A85" s="55"/>
       <c r="B85" s="6">
         <v>84</v>
       </c>
@@ -2944,7 +2944,7 @@
       </c>
     </row>
     <row r="86" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A86" s="48"/>
+      <c r="A86" s="55"/>
       <c r="B86" s="6">
         <v>85</v>
       </c>
@@ -2962,7 +2962,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" ht="25.05" x14ac:dyDescent="0.3">
-      <c r="A87" s="48"/>
+      <c r="A87" s="55"/>
       <c r="B87" s="6">
         <v>86</v>
       </c>
@@ -2980,7 +2980,7 @@
       </c>
     </row>
     <row r="88" spans="1:6" ht="25.7" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="49"/>
+      <c r="A88" s="56"/>
       <c r="B88" s="38">
         <v>87</v>
       </c>
